--- a/work-in-progress/Peppol Code Lists - Document types v9.7.xlsx
+++ b/work-in-progress/Peppol Code Lists - Document types v9.7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\git-peppol\peppol-edec-codelists\work-in-progress\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philip/dev/git-peppol/edec-codelists/work-in-progress/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F070D42-4917-487C-AAC4-157E35102D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DBE495-88C1-6340-8ABD-B0E6C889A0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22110" yWindow="0" windowWidth="19170" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Document Type" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="899">
   <si>
     <t>urn:oasis:names:specification:ubl:schema:xsd:ApplicationResponse-2::ApplicationResponse##urn:www.cenbii.eu:transaction:biicoretrdm057:ver1.0:#urn:www.peppol.eu:bis:peppol1a:ver1.0::2.0</t>
   </si>
@@ -2827,6 +2827,27 @@
   </si>
   <si>
     <t>TICC-437</t>
+  </si>
+  <si>
+    <t>cenbii-procid-ubl::urn:fdc:peppol.eu:2017:poacc:billing:01:1.0
+cenbii-procid-ubl::urn:peppol:bis:billing_with_response
+cenbii-procid-ubl::urn:peppol:france:billing:regulated
+cenbii-procid-ubl::urn:peppol:france:billing:non-regulated</t>
+  </si>
+  <si>
+    <t>cenbii-procid-ubl::urn:fdc:peppol.eu:2017:poacc:selfbilling:01:1.0
+cenbii-procid-ubl::urn:peppol:bis:billing_with_response
+cenbii-procid-ubl::urn:peppol:france:billing:regulated
+cenbii-procid-ubl::urn:peppol:france:billing:non-regulated</t>
+  </si>
+  <si>
+    <t>TICC-359
+TICC-365
+TICC-454</t>
+  </si>
+  <si>
+    <t>TICC-365
+TICC-454</t>
   </si>
 </sst>
 </file>
@@ -3500,26 +3521,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F45987FB-91F4-488D-A9D3-2F3FAED3E07C}">
   <dimension ref="A1:N321"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="97.28515625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="97.33203125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="6" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="43" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="20"/>
-    <col min="12" max="12" width="19.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.140625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="84.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="5"/>
+    <col min="7" max="7" width="15.5" style="43" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="5" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" style="20"/>
+    <col min="12" max="12" width="19.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.1640625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="84.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.5" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>117</v>
       </c>
@@ -3563,7 +3584,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
@@ -3603,7 +3624,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="27" t="s">
         <v>8</v>
       </c>
@@ -3643,7 +3664,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="27" t="s">
         <v>9</v>
       </c>
@@ -3683,7 +3704,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="31" t="s">
         <v>96</v>
       </c>
@@ -3723,7 +3744,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="31" t="s">
         <v>98</v>
       </c>
@@ -3763,7 +3784,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="31" t="s">
         <v>98</v>
       </c>
@@ -3803,7 +3824,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="31" t="s">
         <v>36</v>
       </c>
@@ -3843,7 +3864,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="27" t="s">
         <v>28</v>
       </c>
@@ -3883,7 +3904,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="27" t="s">
         <v>331</v>
       </c>
@@ -3926,7 +3947,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="27" t="s">
         <v>29</v>
       </c>
@@ -3966,7 +3987,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="27" t="s">
         <v>25</v>
       </c>
@@ -4006,7 +4027,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="27" t="s">
         <v>26</v>
       </c>
@@ -4046,7 +4067,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="27" t="s">
         <v>97</v>
       </c>
@@ -4086,7 +4107,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="27" t="s">
         <v>727</v>
       </c>
@@ -4126,7 +4147,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="27" t="s">
         <v>97</v>
       </c>
@@ -4166,7 +4187,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="17" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="27" t="s">
         <v>89</v>
       </c>
@@ -4206,7 +4227,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="27" t="s">
         <v>728</v>
       </c>
@@ -4246,7 +4267,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="19" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="31" t="s">
         <v>93</v>
       </c>
@@ -4286,7 +4307,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" s="31" t="s">
         <v>94</v>
       </c>
@@ -4326,7 +4347,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="31" t="s">
         <v>94</v>
       </c>
@@ -4366,7 +4387,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="31" t="s">
         <v>95</v>
       </c>
@@ -4406,7 +4427,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="31" t="s">
         <v>729</v>
       </c>
@@ -4446,7 +4467,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="31" t="s">
         <v>95</v>
       </c>
@@ -4486,7 +4507,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A25" s="31" t="s">
         <v>34</v>
       </c>
@@ -4524,7 +4545,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>35</v>
       </c>
@@ -4557,7 +4578,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A27" s="31" t="s">
         <v>91</v>
       </c>
@@ -4597,7 +4618,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="28" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A28" s="31" t="s">
         <v>328</v>
       </c>
@@ -4640,7 +4661,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" s="31" t="s">
         <v>92</v>
       </c>
@@ -4680,7 +4701,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A30" s="31" t="s">
         <v>39</v>
       </c>
@@ -4720,7 +4741,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A31" s="31" t="s">
         <v>40</v>
       </c>
@@ -4760,7 +4781,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>438</v>
       </c>
@@ -4777,7 +4798,7 @@
         <v>345</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>710</v>
+        <v>898</v>
       </c>
       <c r="I32" s="5" t="b">
         <v>0</v>
@@ -4796,10 +4817,10 @@
         <v>668</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>732</v>
       </c>
@@ -4838,7 +4859,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>90</v>
       </c>
@@ -4871,7 +4892,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="35" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A35" s="31" t="s">
         <v>325</v>
       </c>
@@ -4912,7 +4933,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>118</v>
       </c>
@@ -4948,7 +4969,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>439</v>
       </c>
@@ -4984,7 +5005,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="38" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A38" s="31" t="s">
         <v>454</v>
       </c>
@@ -5027,7 +5048,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="39" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A39" s="31" t="s">
         <v>453</v>
       </c>
@@ -5070,7 +5091,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="40" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A40" s="31" t="s">
         <v>452</v>
       </c>
@@ -5113,7 +5134,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A41" s="31" t="s">
         <v>451</v>
       </c>
@@ -5156,7 +5177,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A42" s="31" t="s">
         <v>450</v>
       </c>
@@ -5199,7 +5220,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="31" t="s">
         <v>449</v>
       </c>
@@ -5242,7 +5263,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="44" spans="1:14" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A44" s="13" t="s">
         <v>99</v>
       </c>
@@ -5285,7 +5306,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="45" spans="1:14" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
         <v>730</v>
       </c>
@@ -5328,7 +5349,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="46" spans="1:14" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
         <v>100</v>
       </c>
@@ -5371,7 +5392,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="47" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A47" s="13" t="s">
         <v>61</v>
       </c>
@@ -5414,7 +5435,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="48" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A48" s="13" t="s">
         <v>62</v>
       </c>
@@ -5457,7 +5478,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="49" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A49" s="31" t="s">
         <v>63</v>
       </c>
@@ -5500,7 +5521,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="50" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="31" t="s">
         <v>64</v>
       </c>
@@ -5543,7 +5564,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="51" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A51" s="31" t="s">
         <v>428</v>
       </c>
@@ -5583,7 +5604,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>429</v>
       </c>
@@ -5619,7 +5640,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>430</v>
       </c>
@@ -5655,7 +5676,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>431</v>
       </c>
@@ -5694,7 +5715,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>432</v>
       </c>
@@ -5733,7 +5754,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>434</v>
       </c>
@@ -5769,7 +5790,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>433</v>
       </c>
@@ -5805,7 +5826,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>435</v>
       </c>
@@ -5841,7 +5862,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>436</v>
       </c>
@@ -5877,7 +5898,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>437</v>
       </c>
@@ -5913,7 +5934,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
         <v>79</v>
       </c>
@@ -5946,7 +5967,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>731</v>
       </c>
@@ -5979,7 +6000,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>440</v>
       </c>
@@ -6015,7 +6036,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="64" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A64" s="31" t="s">
         <v>326</v>
       </c>
@@ -6058,7 +6079,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>441</v>
       </c>
@@ -6097,7 +6118,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="66" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A66" s="13" t="s">
         <v>84</v>
       </c>
@@ -6140,7 +6161,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="67" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A67" s="13" t="s">
         <v>733</v>
       </c>
@@ -6183,7 +6204,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="68" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A68" s="13" t="s">
         <v>85</v>
       </c>
@@ -6226,7 +6247,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>101</v>
       </c>
@@ -6262,7 +6283,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>102</v>
       </c>
@@ -6298,7 +6319,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>106</v>
       </c>
@@ -6334,7 +6355,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="72" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A72" s="13" t="s">
         <v>442</v>
       </c>
@@ -6379,7 +6400,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="73" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A73" s="13" t="s">
         <v>734</v>
       </c>
@@ -6424,7 +6445,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="74" spans="1:14" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" s="13" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A74" s="13" t="s">
         <v>112</v>
       </c>
@@ -6467,7 +6488,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:14" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" s="13" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A75" s="13" t="s">
         <v>735</v>
       </c>
@@ -6510,7 +6531,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="76" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A76" s="13" t="s">
         <v>153</v>
       </c>
@@ -6553,7 +6574,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="77" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A77" s="13" t="s">
         <v>156</v>
       </c>
@@ -6596,7 +6617,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="78" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A78" s="13" t="s">
         <v>158</v>
       </c>
@@ -6639,7 +6660,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="79" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A79" s="13" t="s">
         <v>736</v>
       </c>
@@ -6682,7 +6703,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="80" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A80" s="13" t="s">
         <v>159</v>
       </c>
@@ -6725,7 +6746,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="81" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A81" s="31" t="s">
         <v>162</v>
       </c>
@@ -6768,7 +6789,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="82" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A82" s="31" t="s">
         <v>738</v>
       </c>
@@ -6811,7 +6832,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="83" spans="1:14" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A83" s="13" t="s">
         <v>225</v>
       </c>
@@ -6854,7 +6875,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="84" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A84" s="31" t="s">
         <v>163</v>
       </c>
@@ -6897,7 +6918,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="85" spans="1:14" s="13" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" s="13" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A85" s="13" t="s">
         <v>166</v>
       </c>
@@ -6940,7 +6961,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="86" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" s="13" t="s">
         <v>737</v>
       </c>
@@ -6983,7 +7004,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="87" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A87" s="13" t="s">
         <v>167</v>
       </c>
@@ -7026,7 +7047,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
         <v>172</v>
       </c>
@@ -7062,7 +7083,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="89" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A89" s="31" t="s">
         <v>216</v>
       </c>
@@ -7103,7 +7124,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A90" s="31" t="s">
         <v>217</v>
       </c>
@@ -7144,7 +7165,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="91" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A91" s="31" t="s">
         <v>218</v>
       </c>
@@ -7185,7 +7206,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A92" s="31" t="s">
         <v>219</v>
       </c>
@@ -7226,7 +7247,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
         <v>184</v>
       </c>
@@ -7262,7 +7283,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>740</v>
       </c>
@@ -7298,7 +7319,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
         <v>185</v>
       </c>
@@ -7334,7 +7355,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A96" s="31" t="s">
         <v>190</v>
       </c>
@@ -7377,7 +7398,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A97" s="31" t="s">
         <v>739</v>
       </c>
@@ -7420,7 +7441,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="98" spans="1:14" s="13" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" s="13" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A98" s="13" t="s">
         <v>228</v>
       </c>
@@ -7463,7 +7484,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="99" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A99" s="31" t="s">
         <v>191</v>
       </c>
@@ -7506,7 +7527,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="100" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
         <v>205</v>
       </c>
@@ -7542,7 +7563,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
         <v>206</v>
       </c>
@@ -7578,7 +7599,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="102" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A102" s="8" t="s">
         <v>207</v>
       </c>
@@ -7614,7 +7635,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="103" spans="1:14" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A103" s="13" t="s">
         <v>215</v>
       </c>
@@ -7655,7 +7676,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
         <v>173</v>
       </c>
@@ -7691,7 +7712,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="105" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
         <v>174</v>
       </c>
@@ -7727,7 +7748,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="106" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
         <v>175</v>
       </c>
@@ -7763,7 +7784,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
         <v>176</v>
       </c>
@@ -7799,7 +7820,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>233</v>
       </c>
@@ -7835,7 +7856,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="109" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>234</v>
       </c>
@@ -7871,7 +7892,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="110" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>235</v>
       </c>
@@ -7907,7 +7928,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="111" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>236</v>
       </c>
@@ -7943,7 +7964,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="112" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>237</v>
       </c>
@@ -7979,7 +8000,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>238</v>
       </c>
@@ -8015,7 +8036,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>239</v>
       </c>
@@ -8051,7 +8072,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="115" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>240</v>
       </c>
@@ -8087,7 +8108,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="116" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>241</v>
       </c>
@@ -8123,7 +8144,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>242</v>
       </c>
@@ -8159,7 +8180,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="118" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>243</v>
       </c>
@@ -8195,7 +8216,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="119" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>244</v>
       </c>
@@ -8231,7 +8252,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="120" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>245</v>
       </c>
@@ -8267,7 +8288,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="121" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>246</v>
       </c>
@@ -8303,7 +8324,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="122" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>247</v>
       </c>
@@ -8339,7 +8360,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="123" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>248</v>
       </c>
@@ -8375,7 +8396,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>249</v>
       </c>
@@ -8411,7 +8432,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="125" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>250</v>
       </c>
@@ -8447,7 +8468,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="126" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>251</v>
       </c>
@@ -8483,7 +8504,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>252</v>
       </c>
@@ -8519,7 +8540,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="128" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>253</v>
       </c>
@@ -8555,7 +8576,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="129" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>254</v>
       </c>
@@ -8591,7 +8612,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="130" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
         <v>443</v>
       </c>
@@ -8629,7 +8650,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="131" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
         <v>444</v>
       </c>
@@ -8667,7 +8688,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="132" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
         <v>445</v>
       </c>
@@ -8705,7 +8726,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="133" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
         <v>446</v>
       </c>
@@ -8743,7 +8764,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="134" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
         <v>287</v>
       </c>
@@ -8778,7 +8799,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="135" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A135" s="5" t="s">
         <v>288</v>
       </c>
@@ -8813,7 +8834,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="136" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="s">
         <v>289</v>
       </c>
@@ -8848,7 +8869,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="137" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A137" s="5" t="s">
         <v>290</v>
       </c>
@@ -8883,7 +8904,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="138" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
         <v>291</v>
       </c>
@@ -8918,7 +8939,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="139" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
         <v>292</v>
       </c>
@@ -8953,7 +8974,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="140" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="s">
         <v>293</v>
       </c>
@@ -8988,7 +9009,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="141" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
         <v>294</v>
       </c>
@@ -9023,7 +9044,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="142" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A142" s="5" t="s">
         <v>295</v>
       </c>
@@ -9058,7 +9079,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="143" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A143" s="5" t="s">
         <v>296</v>
       </c>
@@ -9093,7 +9114,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="144" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
         <v>297</v>
       </c>
@@ -9128,7 +9149,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="145" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A145" s="5" t="s">
         <v>298</v>
       </c>
@@ -9163,7 +9184,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="146" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A146" s="5" t="s">
         <v>299</v>
       </c>
@@ -9198,7 +9219,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="147" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
         <v>300</v>
       </c>
@@ -9233,7 +9254,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="148" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A148" s="31" t="s">
         <v>332</v>
       </c>
@@ -9275,7 +9296,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="149" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A149" s="31" t="s">
         <v>741</v>
       </c>
@@ -9317,7 +9338,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="150" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A150" s="31" t="s">
         <v>333</v>
       </c>
@@ -9359,7 +9380,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="151" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A151" s="31" t="s">
         <v>337</v>
       </c>
@@ -9401,7 +9422,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="152" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A152" s="31" t="s">
         <v>742</v>
       </c>
@@ -9443,7 +9464,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="153" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A153" s="31" t="s">
         <v>338</v>
       </c>
@@ -9485,7 +9506,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="154" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A154" s="5" t="s">
         <v>353</v>
       </c>
@@ -9520,7 +9541,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="155" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A155" s="5" t="s">
         <v>354</v>
       </c>
@@ -9555,7 +9576,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="156" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A156" s="5" t="s">
         <v>355</v>
       </c>
@@ -9590,7 +9611,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="157" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A157" s="5" t="s">
         <v>367</v>
       </c>
@@ -9628,7 +9649,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="158" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A158" s="5" t="s">
         <v>368</v>
       </c>
@@ -9666,7 +9687,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="159" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
         <v>369</v>
       </c>
@@ -9704,7 +9725,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="160" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="5" t="s">
         <v>370</v>
       </c>
@@ -9742,7 +9763,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="5" t="s">
         <v>371</v>
       </c>
@@ -9780,7 +9801,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="162" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
         <v>372</v>
       </c>
@@ -9818,7 +9839,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="163" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A163" s="5" t="s">
         <v>373</v>
       </c>
@@ -9856,7 +9877,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="164" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A164" s="5" t="s">
         <v>374</v>
       </c>
@@ -9894,7 +9915,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="165" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" s="5" t="s">
         <v>375</v>
       </c>
@@ -9932,7 +9953,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="166" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A166" s="5" t="s">
         <v>376</v>
       </c>
@@ -9970,7 +9991,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" s="5" t="s">
         <v>377</v>
       </c>
@@ -10008,7 +10029,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="168" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A168" s="5" t="s">
         <v>378</v>
       </c>
@@ -10046,7 +10067,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="169" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A169" s="5" t="s">
         <v>379</v>
       </c>
@@ -10084,7 +10105,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="170" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A170" s="5" t="s">
         <v>380</v>
       </c>
@@ -10122,7 +10143,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="171" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" s="5" t="s">
         <v>383</v>
       </c>
@@ -10160,7 +10181,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="172" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A172" s="5" t="s">
         <v>382</v>
       </c>
@@ -10198,7 +10219,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="173" spans="1:14" s="31" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" s="31" customFormat="1" ht="80" x14ac:dyDescent="0.2">
       <c r="A173" s="31" t="s">
         <v>528</v>
       </c>
@@ -10240,7 +10261,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="174" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A174" s="5" t="s">
         <v>381</v>
       </c>
@@ -10278,7 +10299,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="175" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A175" s="31" t="s">
         <v>402</v>
       </c>
@@ -10318,7 +10339,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="176" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A176" s="31" t="s">
         <v>743</v>
       </c>
@@ -10358,7 +10379,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="177" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A177" s="31" t="s">
         <v>403</v>
       </c>
@@ -10398,7 +10419,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="178" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A178" s="31" t="s">
         <v>404</v>
       </c>
@@ -10438,7 +10459,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="179" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A179" s="31" t="s">
         <v>744</v>
       </c>
@@ -10480,7 +10501,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="180" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A180" s="31" t="s">
         <v>405</v>
       </c>
@@ -10520,7 +10541,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="181" spans="1:14" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A181" s="38" t="s">
         <v>447</v>
       </c>
@@ -10562,7 +10583,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="182" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A182" s="38" t="s">
         <v>448</v>
       </c>
@@ -10604,7 +10625,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="183" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A183" s="5" t="s">
         <v>828</v>
       </c>
@@ -10642,7 +10663,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="184" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A184" s="31" t="s">
         <v>829</v>
       </c>
@@ -10684,7 +10705,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="185" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A185" s="5" t="s">
         <v>830</v>
       </c>
@@ -10722,7 +10743,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="186" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A186" s="5" t="s">
         <v>423</v>
       </c>
@@ -10757,7 +10778,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="187" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A187" s="5" t="s">
         <v>455</v>
       </c>
@@ -10792,7 +10813,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="188" spans="1:14" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A188" s="38" t="s">
         <v>458</v>
       </c>
@@ -10837,7 +10858,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="189" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A189" s="5" t="s">
         <v>466</v>
       </c>
@@ -10875,7 +10896,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="190" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A190" s="5" t="s">
         <v>467</v>
       </c>
@@ -10913,7 +10934,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="191" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A191" s="5" t="s">
         <v>468</v>
       </c>
@@ -10951,7 +10972,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="192" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A192" s="31" t="s">
         <v>481</v>
       </c>
@@ -10991,7 +11012,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="193" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A193" s="31" t="s">
         <v>746</v>
       </c>
@@ -11031,7 +11052,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="194" spans="1:14" s="31" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A194" s="31" t="s">
         <v>482</v>
       </c>
@@ -11071,7 +11092,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="195" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A195" s="31" t="s">
         <v>483</v>
       </c>
@@ -11111,7 +11132,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="196" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A196" s="31" t="s">
         <v>747</v>
       </c>
@@ -11153,7 +11174,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="197" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A197" s="31" t="s">
         <v>484</v>
       </c>
@@ -11193,7 +11214,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="198" spans="1:14" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A198" s="38" t="s">
         <v>490</v>
       </c>
@@ -11238,7 +11259,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="199" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A199" s="5" t="s">
         <v>494</v>
       </c>
@@ -11277,7 +11298,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="200" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A200" s="5" t="s">
         <v>495</v>
       </c>
@@ -11316,7 +11337,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="201" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A201" s="5" t="s">
         <v>499</v>
       </c>
@@ -11355,7 +11376,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="202" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A202" s="5" t="s">
         <v>500</v>
       </c>
@@ -11394,7 +11415,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="203" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A203" s="5" t="s">
         <v>504</v>
       </c>
@@ -11432,7 +11453,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="204" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A204" s="5" t="s">
         <v>505</v>
       </c>
@@ -11470,7 +11491,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A205" s="5" t="s">
         <v>509</v>
       </c>
@@ -11508,7 +11529,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="206" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A206" s="5" t="s">
         <v>510</v>
       </c>
@@ -11546,7 +11567,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A207" s="5" t="s">
         <v>515</v>
       </c>
@@ -11584,7 +11605,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="208" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A208" s="5" t="s">
         <v>514</v>
       </c>
@@ -11622,7 +11643,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="209" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" s="5" t="s">
         <v>519</v>
       </c>
@@ -11660,7 +11681,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="210" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A210" s="5" t="s">
         <v>520</v>
       </c>
@@ -11698,7 +11719,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="211" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A211" s="5" t="s">
         <v>530</v>
       </c>
@@ -11736,7 +11757,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="212" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A212" s="5" t="s">
         <v>532</v>
       </c>
@@ -11774,7 +11795,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="213" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A213" s="5" t="s">
         <v>533</v>
       </c>
@@ -11812,7 +11833,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="214" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A214" s="38" t="s">
         <v>831</v>
       </c>
@@ -11856,7 +11877,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="215" spans="1:14" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A215" s="38" t="s">
         <v>832</v>
       </c>
@@ -11900,7 +11921,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="216" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A216" s="5" t="s">
         <v>833</v>
       </c>
@@ -11938,7 +11959,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="217" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A217" s="5" t="s">
         <v>834</v>
       </c>
@@ -11976,7 +11997,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="218" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A218" s="5" t="s">
         <v>835</v>
       </c>
@@ -12014,7 +12035,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="219" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A219" s="5" t="s">
         <v>836</v>
       </c>
@@ -12052,7 +12073,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A220" s="5" t="s">
         <v>551</v>
       </c>
@@ -12087,7 +12108,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="221" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A221" s="5" t="s">
         <v>556</v>
       </c>
@@ -12122,7 +12143,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="222" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A222" s="5" t="s">
         <v>557</v>
       </c>
@@ -12157,7 +12178,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A223" s="5" t="s">
         <v>567</v>
       </c>
@@ -12195,7 +12216,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A224" s="5" t="s">
         <v>745</v>
       </c>
@@ -12233,7 +12254,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="225" spans="1:14" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A225" s="38" t="s">
         <v>570</v>
       </c>
@@ -12277,7 +12298,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>570</v>
       </c>
@@ -12315,7 +12336,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>490</v>
       </c>
@@ -12353,7 +12374,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="228" spans="1:14" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A228" s="38" t="s">
         <v>571</v>
       </c>
@@ -12397,7 +12418,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="229" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>571</v>
       </c>
@@ -12435,7 +12456,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="230" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A230" s="13" t="s">
         <v>573</v>
       </c>
@@ -12479,7 +12500,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="231" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A231" s="13" t="s">
         <v>575</v>
       </c>
@@ -12523,7 +12544,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="232" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A232" s="13" t="s">
         <v>577</v>
       </c>
@@ -12567,7 +12588,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="233" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A233" s="13" t="s">
         <v>579</v>
       </c>
@@ -12611,7 +12632,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A234" s="5" t="s">
         <v>573</v>
       </c>
@@ -12649,7 +12670,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="235" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A235" s="5" t="s">
         <v>575</v>
       </c>
@@ -12687,7 +12708,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="236" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A236" s="5" t="s">
         <v>577</v>
       </c>
@@ -12725,7 +12746,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="237" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A237" s="5" t="s">
         <v>579</v>
       </c>
@@ -12763,7 +12784,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="238" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A238" s="5" t="s">
         <v>584</v>
       </c>
@@ -12798,7 +12819,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="239" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A239" s="5" t="s">
         <v>748</v>
       </c>
@@ -12833,7 +12854,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="240" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A240" s="5" t="s">
         <v>585</v>
       </c>
@@ -12868,7 +12889,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="241" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A241" s="5" t="s">
         <v>586</v>
       </c>
@@ -12903,7 +12924,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="242" spans="1:14" s="31" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A242" s="31" t="s">
         <v>749</v>
       </c>
@@ -12945,7 +12966,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="243" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A243" s="5" t="s">
         <v>587</v>
       </c>
@@ -12980,7 +13001,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A244" s="5" t="s">
         <v>597</v>
       </c>
@@ -13018,7 +13039,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="245" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A245" s="5" t="s">
         <v>596</v>
       </c>
@@ -13056,7 +13077,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>608</v>
       </c>
@@ -13094,7 +13115,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="247" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>609</v>
       </c>
@@ -13132,7 +13153,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>610</v>
       </c>
@@ -13170,7 +13191,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="249" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>611</v>
       </c>
@@ -13208,7 +13229,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="250" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A250" s="13" t="s">
         <v>608</v>
       </c>
@@ -13252,7 +13273,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="251" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A251" s="13" t="s">
         <v>609</v>
       </c>
@@ -13296,7 +13317,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="252" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A252" s="13" t="s">
         <v>610</v>
       </c>
@@ -13340,7 +13361,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="253" spans="1:14" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A253" s="13" t="s">
         <v>611</v>
       </c>
@@ -13384,7 +13405,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A254" s="5" t="s">
         <v>618</v>
       </c>
@@ -13419,7 +13440,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A255" s="5" t="s">
         <v>623</v>
       </c>
@@ -13454,7 +13475,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A256" s="5" t="s">
         <v>624</v>
       </c>
@@ -13489,7 +13510,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A257" s="5" t="s">
         <v>626</v>
       </c>
@@ -13524,7 +13545,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A258" s="5" t="s">
         <v>627</v>
       </c>
@@ -13559,7 +13580,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A259" s="5" t="s">
         <v>629</v>
       </c>
@@ -13594,7 +13615,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="260" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A260" s="5" t="s">
         <v>646</v>
       </c>
@@ -13629,7 +13650,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="261" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A261" s="5" t="s">
         <v>647</v>
       </c>
@@ -13664,7 +13685,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="262" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A262" s="5" t="s">
         <v>648</v>
       </c>
@@ -13699,7 +13720,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="263" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A263" s="5" t="s">
         <v>649</v>
       </c>
@@ -13734,7 +13755,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="264" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A264" s="5" t="s">
         <v>650</v>
       </c>
@@ -13769,7 +13790,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="265" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A265" s="5" t="s">
         <v>651</v>
       </c>
@@ -13804,7 +13825,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="266" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A266" s="5" t="s">
         <v>652</v>
       </c>
@@ -13839,7 +13860,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="267" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A267" s="5" t="s">
         <v>653</v>
       </c>
@@ -13874,7 +13895,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="268" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A268" s="5" t="s">
         <v>654</v>
       </c>
@@ -13909,7 +13930,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="269" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A269" s="5" t="s">
         <v>712</v>
       </c>
@@ -13926,7 +13947,7 @@
         <v>345</v>
       </c>
       <c r="H269" s="5" t="s">
-        <v>709</v>
+        <v>897</v>
       </c>
       <c r="I269" s="5" t="b">
         <v>0</v>
@@ -13945,10 +13966,10 @@
         <v>668</v>
       </c>
       <c r="N269" s="5" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="270" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A270" s="5" t="s">
         <v>752</v>
       </c>
@@ -13987,7 +14008,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="271" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A271" s="5" t="s">
         <v>689</v>
       </c>
@@ -14022,7 +14043,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="272" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A272" s="5" t="s">
         <v>704</v>
       </c>
@@ -14061,7 +14082,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="273" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A273" s="5" t="s">
         <v>698</v>
       </c>
@@ -14100,7 +14121,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="274" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A274" s="5" t="s">
         <v>699</v>
       </c>
@@ -14139,7 +14160,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="275" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A275" s="5" t="s">
         <v>700</v>
       </c>
@@ -14178,7 +14199,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="276" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A276" s="5" t="s">
         <v>701</v>
       </c>
@@ -14217,7 +14238,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="277" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A277" s="5" t="s">
         <v>705</v>
       </c>
@@ -14256,7 +14277,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="278" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A278" s="5" t="s">
         <v>750</v>
       </c>
@@ -14295,7 +14316,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="279" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A279" s="5" t="s">
         <v>751</v>
       </c>
@@ -14334,7 +14355,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>717</v>
       </c>
@@ -14373,7 +14394,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="281" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>718</v>
       </c>
@@ -14412,7 +14433,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>719</v>
       </c>
@@ -14451,7 +14472,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="283" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>720</v>
       </c>
@@ -14490,7 +14511,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="284" spans="1:14" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A284" s="13" t="s">
         <v>802</v>
       </c>
@@ -14533,7 +14554,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="285" spans="1:14" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A285" s="13" t="s">
         <v>803</v>
       </c>
@@ -14576,7 +14597,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="286" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A286" s="5" t="s">
         <v>759</v>
       </c>
@@ -14612,7 +14633,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="287" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A287" s="5" t="s">
         <v>760</v>
       </c>
@@ -14648,7 +14669,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="288" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A288" s="5" t="s">
         <v>762</v>
       </c>
@@ -14684,7 +14705,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="289" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A289" s="5" t="s">
         <v>765</v>
       </c>
@@ -14720,7 +14741,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="290" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A290" s="5" t="s">
         <v>767</v>
       </c>
@@ -14756,7 +14777,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="291" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A291" s="5" t="s">
         <v>769</v>
       </c>
@@ -14792,7 +14813,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="292" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A292" s="5" t="s">
         <v>771</v>
       </c>
@@ -14828,7 +14849,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="293" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A293" s="5" t="s">
         <v>772</v>
       </c>
@@ -14864,7 +14885,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="294" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A294" s="5" t="s">
         <v>773</v>
       </c>
@@ -14900,7 +14921,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="295" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A295" s="5" t="s">
         <v>774</v>
       </c>
@@ -14936,7 +14957,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A296" s="5" t="s">
         <v>778</v>
       </c>
@@ -14972,7 +14993,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A297" s="5" t="s">
         <v>781</v>
       </c>
@@ -15008,7 +15029,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="298" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A298" s="5" t="s">
         <v>783</v>
       </c>
@@ -15044,7 +15065,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="299" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A299" s="5" t="s">
         <v>785</v>
       </c>
@@ -15080,7 +15101,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="300" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A300" s="5" t="s">
         <v>787</v>
       </c>
@@ -15116,7 +15137,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="301" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A301" s="5" t="s">
         <v>789</v>
       </c>
@@ -15152,7 +15173,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A302" s="5" t="s">
         <v>791</v>
       </c>
@@ -15188,7 +15209,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="303" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A303" s="5" t="s">
         <v>804</v>
       </c>
@@ -15223,7 +15244,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="304" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A304" s="5" t="s">
         <v>808</v>
       </c>
@@ -15259,7 +15280,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="305" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A305" s="5" t="s">
         <v>818</v>
       </c>
@@ -15294,7 +15315,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>819</v>
       </c>
@@ -15333,7 +15354,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="307" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>820</v>
       </c>
@@ -15372,7 +15393,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="308" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>840</v>
       </c>
@@ -15411,7 +15432,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="309" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A309" s="5" t="s">
         <v>841</v>
       </c>
@@ -15449,7 +15470,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="310" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A310" s="5" t="s">
         <v>842</v>
       </c>
@@ -15487,7 +15508,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>846</v>
       </c>
@@ -15525,7 +15546,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="312" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>847</v>
       </c>
@@ -15563,7 +15584,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>848</v>
       </c>
@@ -15601,7 +15622,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="314" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>849</v>
       </c>
@@ -15639,7 +15660,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>802</v>
       </c>
@@ -15676,7 +15697,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>881</v>
       </c>
@@ -15714,7 +15735,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="317" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>882</v>
       </c>
@@ -15752,7 +15773,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="318" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>883</v>
       </c>
@@ -15790,7 +15811,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="319" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>884</v>
       </c>
@@ -15828,7 +15849,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>890</v>
       </c>
@@ -15865,7 +15886,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>892</v>
       </c>

--- a/work-in-progress/Peppol Code Lists - Document types v9.7.xlsx
+++ b/work-in-progress/Peppol Code Lists - Document types v9.7.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philip/dev/git-peppol/edec-codelists/work-in-progress/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DBE495-88C1-6340-8ABD-B0E6C889A0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5AFE61-6A44-DE42-A483-007876BE5BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="896">
   <si>
     <t>urn:oasis:names:specification:ubl:schema:xsd:ApplicationResponse-2::ApplicationResponse##urn:www.cenbii.eu:transaction:biicoretrdm057:ver1.0:#urn:www.peppol.eu:bis:peppol1a:ver1.0::2.0</t>
   </si>
@@ -2217,20 +2217,6 @@
   </si>
   <si>
     <t>urn:un:unece:uncefact:data:standard:CrossIndustryInvoice:100::CrossIndustryInvoice##urn:cen.eu:en16931:2017#compliant#urn:peppol:france:billing:cius:1.0::D22B</t>
-  </si>
-  <si>
-    <t>cenbii-procid-ubl::urn:fdc:peppol.eu:2017:poacc:billing:01:1.0
-cenbii-procid-ubl::urn:peppol:france:billing:regulated
-cenbii-procid-ubl::urn:peppol:france:billing:non-regulated</t>
-  </si>
-  <si>
-    <t>cenbii-procid-ubl::urn:fdc:peppol.eu:2017:poacc:selfbilling:01:1.0
-cenbii-procid-ubl::urn:peppol:france:billing:regulated
-cenbii-procid-ubl::urn:peppol:france:billing:non-regulated</t>
-  </si>
-  <si>
-    <t>TICC-359
-TICC-365</t>
   </si>
   <si>
     <t>TICC-365</t>
@@ -3557,7 +3543,7 @@
         <v>343</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G1" s="41" t="s">
         <v>393</v>
@@ -4109,7 +4095,7 @@
     </row>
     <row r="15" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="27" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>56</v>
@@ -4229,7 +4215,7 @@
     </row>
     <row r="18" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="27" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B18" s="27" t="s">
         <v>56</v>
@@ -4429,7 +4415,7 @@
     </row>
     <row r="23" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="31" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B23" s="27" t="s">
         <v>56</v>
@@ -4798,7 +4784,7 @@
         <v>345</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="I32" s="5" t="b">
         <v>0</v>
@@ -4817,12 +4803,12 @@
         <v>668</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="48" x14ac:dyDescent="0.2">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>56</v>
@@ -4837,7 +4823,7 @@
         <v>345</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>710</v>
+        <v>895</v>
       </c>
       <c r="I33" s="5" t="b">
         <v>0</v>
@@ -4856,7 +4842,7 @@
         <v>669</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>707</v>
+        <v>892</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="48" x14ac:dyDescent="0.2">
@@ -5308,7 +5294,7 @@
     </row>
     <row r="45" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>56</v>
@@ -5409,13 +5395,13 @@
         <v>470</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="G47" s="44">
         <v>46025</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="I47" s="13" t="b">
         <v>0</v>
@@ -5452,13 +5438,13 @@
         <v>470</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="G48" s="44">
         <v>46025</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="I48" s="13" t="b">
         <v>0</v>
@@ -5495,13 +5481,13 @@
         <v>344</v>
       </c>
       <c r="F49" s="33" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="G49" s="42">
         <v>46210</v>
       </c>
       <c r="H49" s="31" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="I49" s="31" t="b">
         <v>0</v>
@@ -5538,13 +5524,13 @@
         <v>344</v>
       </c>
       <c r="F50" s="33" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="G50" s="42">
         <v>46210</v>
       </c>
       <c r="H50" s="31" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="I50" s="31" t="b">
         <v>0</v>
@@ -5732,7 +5718,7 @@
         <v>345</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="I55" s="5" t="b">
         <v>0</v>
@@ -5751,7 +5737,7 @@
         <v>675</v>
       </c>
       <c r="N55" s="5" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="16" x14ac:dyDescent="0.2">
@@ -5969,7 +5955,7 @@
     </row>
     <row r="62" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>56</v>
@@ -6163,7 +6149,7 @@
     </row>
     <row r="67" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A67" s="13" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>56</v>
@@ -6372,13 +6358,13 @@
         <v>470</v>
       </c>
       <c r="F72" s="17" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="G72" s="44">
         <v>46112</v>
       </c>
       <c r="H72" s="13" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="I72" s="13" t="b">
         <v>0</v>
@@ -6402,7 +6388,7 @@
     </row>
     <row r="73" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A73" s="13" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>56</v>
@@ -6417,13 +6403,13 @@
         <v>470</v>
       </c>
       <c r="F73" s="17" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="G73" s="44">
         <v>46112</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="I73" s="13" t="b">
         <v>0</v>
@@ -6462,13 +6448,13 @@
         <v>470</v>
       </c>
       <c r="F74" s="17" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="G74" s="44">
         <v>46112</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="I74" s="13" t="b">
         <v>0</v>
@@ -6490,7 +6476,7 @@
     </row>
     <row r="75" spans="1:14" s="13" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A75" s="13" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>56</v>
@@ -6505,13 +6491,13 @@
         <v>470</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="G75" s="44">
         <v>46112</v>
       </c>
       <c r="H75" s="13" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="I75" s="13" t="b">
         <v>0</v>
@@ -6662,7 +6648,7 @@
     </row>
     <row r="79" spans="1:14" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A79" s="13" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>56</v>
@@ -6763,13 +6749,13 @@
         <v>344</v>
       </c>
       <c r="F81" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G81" s="45">
         <v>46235</v>
       </c>
       <c r="H81" s="31" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="I81" s="31" t="b">
         <v>0</v>
@@ -6791,7 +6777,7 @@
     </row>
     <row r="82" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A82" s="31" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B82" s="27" t="s">
         <v>56</v>
@@ -6806,13 +6792,13 @@
         <v>344</v>
       </c>
       <c r="F82" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G82" s="45">
         <v>46235</v>
       </c>
       <c r="H82" s="31" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="I82" s="31" t="b">
         <v>0</v>
@@ -6892,13 +6878,13 @@
         <v>344</v>
       </c>
       <c r="F84" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G84" s="45">
         <v>46235</v>
       </c>
       <c r="H84" s="31" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="I84" s="31" t="b">
         <v>0</v>
@@ -6963,7 +6949,7 @@
     </row>
     <row r="86" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" s="13" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>56</v>
@@ -7206,7 +7192,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A92" s="31" t="s">
         <v>219</v>
       </c>
@@ -7285,7 +7271,7 @@
     </row>
     <row r="94" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>56</v>
@@ -7372,13 +7358,13 @@
         <v>344</v>
       </c>
       <c r="F96" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G96" s="42">
         <v>46235</v>
       </c>
       <c r="H96" s="31" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="I96" s="31" t="b">
         <v>0</v>
@@ -7400,7 +7386,7 @@
     </row>
     <row r="97" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A97" s="31" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B97" s="27" t="s">
         <v>56</v>
@@ -7415,13 +7401,13 @@
         <v>344</v>
       </c>
       <c r="F97" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G97" s="42">
         <v>46235</v>
       </c>
       <c r="H97" s="31" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="I97" s="31" t="b">
         <v>0</v>
@@ -7501,13 +7487,13 @@
         <v>344</v>
       </c>
       <c r="F99" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G99" s="42">
         <v>46235</v>
       </c>
       <c r="H99" s="31" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="I99" s="31" t="b">
         <v>0</v>
@@ -7784,7 +7770,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="48" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
         <v>176</v>
       </c>
@@ -9271,13 +9257,13 @@
         <v>344</v>
       </c>
       <c r="F148" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G148" s="42">
         <v>46235</v>
       </c>
       <c r="H148" s="31" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="I148" s="31" t="b">
         <v>0</v>
@@ -9298,7 +9284,7 @@
     </row>
     <row r="149" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A149" s="31" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B149" s="27" t="s">
         <v>56</v>
@@ -9313,13 +9299,13 @@
         <v>344</v>
       </c>
       <c r="F149" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G149" s="42">
         <v>46235</v>
       </c>
       <c r="H149" s="31" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="I149" s="31" t="b">
         <v>0</v>
@@ -9355,13 +9341,13 @@
         <v>344</v>
       </c>
       <c r="F150" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G150" s="42">
         <v>46235</v>
       </c>
       <c r="H150" s="31" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="I150" s="31" t="b">
         <v>0</v>
@@ -9397,13 +9383,13 @@
         <v>344</v>
       </c>
       <c r="F151" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G151" s="42">
         <v>46235</v>
       </c>
       <c r="H151" s="31" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="I151" s="31" t="b">
         <v>0</v>
@@ -9424,7 +9410,7 @@
     </row>
     <row r="152" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A152" s="31" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B152" s="27" t="s">
         <v>56</v>
@@ -9439,13 +9425,13 @@
         <v>344</v>
       </c>
       <c r="F152" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G152" s="42">
         <v>46235</v>
       </c>
       <c r="H152" s="31" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="I152" s="31" t="b">
         <v>0</v>
@@ -9481,13 +9467,13 @@
         <v>344</v>
       </c>
       <c r="F153" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G153" s="42">
         <v>46235</v>
       </c>
       <c r="H153" s="31" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="I153" s="31" t="b">
         <v>0</v>
@@ -10316,11 +10302,11 @@
         <v>344</v>
       </c>
       <c r="F175" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G175" s="42"/>
       <c r="H175" s="31" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="I175" s="31" t="b">
         <v>0</v>
@@ -10341,7 +10327,7 @@
     </row>
     <row r="176" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A176" s="31" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B176" s="27" t="s">
         <v>56</v>
@@ -10356,11 +10342,11 @@
         <v>344</v>
       </c>
       <c r="F176" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G176" s="42"/>
       <c r="H176" s="31" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="I176" s="31" t="b">
         <v>0</v>
@@ -10396,11 +10382,11 @@
         <v>344</v>
       </c>
       <c r="F177" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G177" s="42"/>
       <c r="H177" s="31" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="I177" s="31" t="b">
         <v>0</v>
@@ -10436,11 +10422,11 @@
         <v>344</v>
       </c>
       <c r="F178" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G178" s="42"/>
       <c r="H178" s="31" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="I178" s="31" t="b">
         <v>0</v>
@@ -10461,7 +10447,7 @@
     </row>
     <row r="179" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A179" s="31" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B179" s="27" t="s">
         <v>56</v>
@@ -10476,13 +10462,13 @@
         <v>344</v>
       </c>
       <c r="F179" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G179" s="42">
         <v>46235</v>
       </c>
       <c r="H179" s="31" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="I179" s="31" t="b">
         <v>0</v>
@@ -10518,11 +10504,11 @@
         <v>344</v>
       </c>
       <c r="F180" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G180" s="42"/>
       <c r="H180" s="31" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="I180" s="31" t="b">
         <v>0</v>
@@ -10627,7 +10613,7 @@
     </row>
     <row r="183" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A183" s="5" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>56</v>
@@ -10654,10 +10640,10 @@
         <v>1</v>
       </c>
       <c r="L183" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M183" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="N183" s="37" t="s">
         <v>635</v>
@@ -10665,7 +10651,7 @@
     </row>
     <row r="184" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A184" s="31" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B184" s="27" t="s">
         <v>56</v>
@@ -10680,11 +10666,11 @@
         <v>344</v>
       </c>
       <c r="F184" s="33" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G184" s="42"/>
       <c r="H184" s="31" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="I184" s="31" t="b">
         <v>0</v>
@@ -10696,10 +10682,10 @@
         <v>1</v>
       </c>
       <c r="L184" s="27" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M184" s="27" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="N184" s="31" t="s">
         <v>421</v>
@@ -10707,7 +10693,7 @@
     </row>
     <row r="185" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A185" s="5" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>56</v>
@@ -10734,10 +10720,10 @@
         <v>1</v>
       </c>
       <c r="L185" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M185" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="N185" s="12" t="s">
         <v>422</v>
@@ -10989,11 +10975,11 @@
         <v>344</v>
       </c>
       <c r="F192" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G192" s="42"/>
       <c r="H192" s="31" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="I192" s="31" t="b">
         <v>0</v>
@@ -11014,7 +11000,7 @@
     </row>
     <row r="193" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A193" s="31" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B193" s="27" t="s">
         <v>56</v>
@@ -11029,11 +11015,11 @@
         <v>344</v>
       </c>
       <c r="F193" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G193" s="42"/>
       <c r="H193" s="31" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="I193" s="31" t="b">
         <v>0</v>
@@ -11069,11 +11055,11 @@
         <v>344</v>
       </c>
       <c r="F194" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G194" s="42"/>
       <c r="H194" s="31" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="I194" s="31" t="b">
         <v>0</v>
@@ -11109,11 +11095,11 @@
         <v>344</v>
       </c>
       <c r="F195" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G195" s="42"/>
       <c r="H195" s="31" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="I195" s="31" t="b">
         <v>0</v>
@@ -11134,7 +11120,7 @@
     </row>
     <row r="196" spans="1:14" s="31" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A196" s="31" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="B196" s="27" t="s">
         <v>56</v>
@@ -11149,13 +11135,13 @@
         <v>344</v>
       </c>
       <c r="F196" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G196" s="42">
         <v>46235</v>
       </c>
       <c r="H196" s="31" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="I196" s="31" t="b">
         <v>0</v>
@@ -11191,11 +11177,11 @@
         <v>344</v>
       </c>
       <c r="F197" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G197" s="42"/>
       <c r="H197" s="31" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="I197" s="31" t="b">
         <v>0</v>
@@ -11835,7 +11821,7 @@
     </row>
     <row r="214" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A214" s="38" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="B214" s="14" t="s">
         <v>56</v>
@@ -11850,13 +11836,13 @@
         <v>470</v>
       </c>
       <c r="F214" s="18" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="G214" s="44">
         <v>46025</v>
       </c>
       <c r="H214" s="13" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="I214" s="13" t="b">
         <v>0</v>
@@ -11868,10 +11854,10 @@
         <v>1</v>
       </c>
       <c r="L214" s="14" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M214" s="14" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="N214" s="16" t="s">
         <v>539</v>
@@ -11879,7 +11865,7 @@
     </row>
     <row r="215" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A215" s="38" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B215" s="14" t="s">
         <v>56</v>
@@ -11894,13 +11880,13 @@
         <v>470</v>
       </c>
       <c r="F215" s="18" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="G215" s="44">
         <v>46025</v>
       </c>
       <c r="H215" s="13" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="I215" s="13" t="b">
         <v>0</v>
@@ -11912,10 +11898,10 @@
         <v>1</v>
       </c>
       <c r="L215" s="14" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M215" s="14" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="N215" s="16" t="s">
         <v>540</v>
@@ -11923,7 +11909,7 @@
     </row>
     <row r="216" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A216" s="5" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B216" s="4" t="s">
         <v>56</v>
@@ -11950,10 +11936,10 @@
         <v>1</v>
       </c>
       <c r="L216" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M216" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="N216" s="36" t="s">
         <v>541</v>
@@ -11961,7 +11947,7 @@
     </row>
     <row r="217" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A217" s="5" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="B217" s="4" t="s">
         <v>56</v>
@@ -11976,7 +11962,7 @@
         <v>345</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="I217" s="5" t="b">
         <v>0</v>
@@ -11988,18 +11974,18 @@
         <v>1</v>
       </c>
       <c r="L217" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M217" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="N217" s="47" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
     </row>
     <row r="218" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A218" s="5" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="B218" s="4" t="s">
         <v>56</v>
@@ -12014,7 +12000,7 @@
         <v>345</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="I218" s="5" t="b">
         <v>0</v>
@@ -12026,18 +12012,18 @@
         <v>1</v>
       </c>
       <c r="L218" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M218" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="N218" s="47" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
     </row>
     <row r="219" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A219" s="5" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="B219" s="4" t="s">
         <v>56</v>
@@ -12064,10 +12050,10 @@
         <v>1</v>
       </c>
       <c r="L219" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M219" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="N219" s="36" t="s">
         <v>542</v>
@@ -12218,7 +12204,7 @@
     </row>
     <row r="224" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A224" s="5" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B224" s="5" t="s">
         <v>563</v>
@@ -12473,13 +12459,13 @@
         <v>470</v>
       </c>
       <c r="F230" s="39" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="G230" s="44">
         <v>45717</v>
       </c>
       <c r="H230" s="13" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="I230" s="13" t="b">
         <v>0</v>
@@ -12517,13 +12503,13 @@
         <v>470</v>
       </c>
       <c r="F231" s="39" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="G231" s="44">
         <v>45717</v>
       </c>
       <c r="H231" s="13" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="I231" s="13" t="b">
         <v>0</v>
@@ -12561,13 +12547,13 @@
         <v>470</v>
       </c>
       <c r="F232" s="39" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="G232" s="44">
         <v>45717</v>
       </c>
       <c r="H232" s="13" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="I232" s="13" t="b">
         <v>0</v>
@@ -12605,13 +12591,13 @@
         <v>470</v>
       </c>
       <c r="F233" s="39" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="G233" s="44">
         <v>45717</v>
       </c>
       <c r="H233" s="13" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="I233" s="13" t="b">
         <v>0</v>
@@ -12821,7 +12807,7 @@
     </row>
     <row r="239" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A239" s="5" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B239" s="4" t="s">
         <v>56</v>
@@ -12926,7 +12912,7 @@
     </row>
     <row r="242" spans="1:14" s="31" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A242" s="31" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="B242" s="27" t="s">
         <v>56</v>
@@ -12941,13 +12927,13 @@
         <v>344</v>
       </c>
       <c r="F242" s="35" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G242" s="42">
         <v>46235</v>
       </c>
       <c r="H242" s="31" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="I242" s="31" t="b">
         <v>0</v>
@@ -13252,7 +13238,7 @@
         <v>45909</v>
       </c>
       <c r="H250" s="13" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="I250" s="13" t="b">
         <v>0</v>
@@ -13296,7 +13282,7 @@
         <v>45909</v>
       </c>
       <c r="H251" s="13" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="I251" s="13" t="b">
         <v>0</v>
@@ -13340,7 +13326,7 @@
         <v>45909</v>
       </c>
       <c r="H252" s="13" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="I252" s="13" t="b">
         <v>0</v>
@@ -13384,7 +13370,7 @@
         <v>45909</v>
       </c>
       <c r="H253" s="13" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="I253" s="13" t="b">
         <v>0</v>
@@ -13932,7 +13918,7 @@
     </row>
     <row r="269" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A269" s="5" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B269" s="4" t="s">
         <v>56</v>
@@ -13947,7 +13933,7 @@
         <v>345</v>
       </c>
       <c r="H269" s="5" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="I269" s="5" t="b">
         <v>0</v>
@@ -13966,12 +13952,12 @@
         <v>668</v>
       </c>
       <c r="N269" s="5" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="270" spans="1:14" ht="48" x14ac:dyDescent="0.2">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A270" s="5" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B270" s="4" t="s">
         <v>56</v>
@@ -13986,7 +13972,7 @@
         <v>345</v>
       </c>
       <c r="H270" s="5" t="s">
-        <v>709</v>
+        <v>894</v>
       </c>
       <c r="I270" s="5" t="b">
         <v>0</v>
@@ -14005,7 +13991,7 @@
         <v>669</v>
       </c>
       <c r="N270" s="5" t="s">
-        <v>708</v>
+        <v>893</v>
       </c>
     </row>
     <row r="271" spans="1:14" ht="32" x14ac:dyDescent="0.2">
@@ -14279,22 +14265,22 @@
     </row>
     <row r="278" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A278" s="5" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B278" s="4" t="s">
         <v>56</v>
       </c>
       <c r="C278" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="D278" s="24" t="s">
+        <v>712</v>
+      </c>
+      <c r="E278" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="H278" s="5" t="s">
         <v>713</v>
-      </c>
-      <c r="D278" s="24" t="s">
-        <v>715</v>
-      </c>
-      <c r="E278" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="H278" s="5" t="s">
-        <v>716</v>
       </c>
       <c r="I278" s="5" t="b">
         <v>0</v>
@@ -14318,22 +14304,22 @@
     </row>
     <row r="279" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A279" s="5" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B279" s="4" t="s">
         <v>56</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D279" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E279" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H279" s="5" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="I279" s="5" t="b">
         <v>0</v>
@@ -14357,22 +14343,22 @@
     </row>
     <row r="280" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B280" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="D280" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E280" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H280" s="5" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="I280" s="5" t="b">
         <v>0</v>
@@ -14396,22 +14382,22 @@
     </row>
     <row r="281" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B281" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C281" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="D281" s="24" t="s">
+        <v>712</v>
+      </c>
+      <c r="E281" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="H281" s="5" t="s">
         <v>722</v>
-      </c>
-      <c r="D281" s="24" t="s">
-        <v>715</v>
-      </c>
-      <c r="E281" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="H281" s="5" t="s">
-        <v>725</v>
       </c>
       <c r="I281" s="5" t="b">
         <v>0</v>
@@ -14435,22 +14421,22 @@
     </row>
     <row r="282" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="B282" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D282" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E282" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H282" s="5" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="I282" s="5" t="b">
         <v>0</v>
@@ -14474,22 +14460,22 @@
     </row>
     <row r="283" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B283" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D283" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E283" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H283" s="5" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="I283" s="5" t="b">
         <v>0</v>
@@ -14513,28 +14499,28 @@
     </row>
     <row r="284" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A284" s="13" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B284" s="13" t="s">
         <v>563</v>
       </c>
       <c r="C284" s="13" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D284" s="25" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E284" s="21" t="s">
         <v>470</v>
       </c>
       <c r="F284" s="39" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G284" s="44">
         <v>46112</v>
       </c>
       <c r="H284" s="13" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="I284" s="13" t="b">
         <v>0</v>
@@ -14548,36 +14534,36 @@
         <v>111</v>
       </c>
       <c r="M284" s="14" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="N284" s="13" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
     </row>
     <row r="285" spans="1:14" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A285" s="13" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B285" s="13" t="s">
         <v>563</v>
       </c>
       <c r="C285" s="13" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="D285" s="25" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E285" s="21" t="s">
         <v>470</v>
       </c>
       <c r="F285" s="39" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G285" s="44">
         <v>46112</v>
       </c>
       <c r="H285" s="13" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="I285" s="13" t="b">
         <v>0</v>
@@ -14591,30 +14577,30 @@
         <v>111</v>
       </c>
       <c r="M285" s="14" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="N285" s="13" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
     </row>
     <row r="286" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A286" s="5" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B286" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D286" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E286" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H286" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I286" s="5" t="b">
         <v>0</v>
@@ -14624,33 +14610,33 @@
         <v>1</v>
       </c>
       <c r="L286" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M286" s="4" t="s">
         <v>668</v>
       </c>
       <c r="N286" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="287" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A287" s="5" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B287" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D287" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E287" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H287" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I287" s="5" t="b">
         <v>0</v>
@@ -14660,33 +14646,33 @@
         <v>1</v>
       </c>
       <c r="L287" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M287" s="4" t="s">
         <v>669</v>
       </c>
       <c r="N287" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="288" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A288" s="5" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B288" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D288" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E288" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H288" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I288" s="5" t="b">
         <v>0</v>
@@ -14696,33 +14682,33 @@
         <v>1</v>
       </c>
       <c r="L288" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M288" s="4" t="s">
         <v>667</v>
       </c>
       <c r="N288" s="5" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="289" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A289" s="5" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D289" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E289" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H289" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I289" s="5" t="b">
         <v>0</v>
@@ -14732,33 +14718,33 @@
         <v>1</v>
       </c>
       <c r="L289" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M289" s="4" t="s">
         <v>670</v>
       </c>
       <c r="N289" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="290" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A290" s="5" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="B290" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D290" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E290" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H290" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I290" s="5" t="b">
         <v>0</v>
@@ -14768,33 +14754,33 @@
         <v>1</v>
       </c>
       <c r="L290" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M290" s="4" t="s">
         <v>671</v>
       </c>
       <c r="N290" s="5" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="291" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A291" s="5" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D291" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E291" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H291" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I291" s="5" t="b">
         <v>0</v>
@@ -14804,33 +14790,33 @@
         <v>1</v>
       </c>
       <c r="L291" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M291" s="4" t="s">
         <v>668</v>
       </c>
       <c r="N291" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="292" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A292" s="5" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B292" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D292" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E292" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H292" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I292" s="5" t="b">
         <v>0</v>
@@ -14840,33 +14826,33 @@
         <v>1</v>
       </c>
       <c r="L292" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M292" s="4" t="s">
         <v>667</v>
       </c>
       <c r="N292" s="5" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="293" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A293" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C293" s="5" t="s">
         <v>772</v>
       </c>
-      <c r="B293" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C293" s="5" t="s">
-        <v>775</v>
-      </c>
       <c r="D293" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E293" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H293" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I293" s="5" t="b">
         <v>0</v>
@@ -14876,33 +14862,33 @@
         <v>1</v>
       </c>
       <c r="L293" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M293" s="4" t="s">
         <v>670</v>
       </c>
       <c r="N293" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="294" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A294" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C294" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="B294" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C294" s="5" t="s">
-        <v>776</v>
-      </c>
       <c r="D294" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E294" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H294" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I294" s="5" t="b">
         <v>0</v>
@@ -14912,33 +14898,33 @@
         <v>1</v>
       </c>
       <c r="L294" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M294" s="4" t="s">
         <v>671</v>
       </c>
       <c r="N294" s="5" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="295" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A295" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C295" s="5" t="s">
         <v>774</v>
       </c>
-      <c r="B295" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C295" s="5" t="s">
-        <v>777</v>
-      </c>
       <c r="D295" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E295" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H295" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I295" s="5" t="b">
         <v>0</v>
@@ -14948,33 +14934,33 @@
         <v>1</v>
       </c>
       <c r="L295" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M295" s="4" t="s">
         <v>668</v>
       </c>
       <c r="N295" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="296" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A296" s="5" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B296" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D296" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E296" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H296" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I296" s="5" t="b">
         <v>0</v>
@@ -14984,33 +14970,33 @@
         <v>1</v>
       </c>
       <c r="L296" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M296" s="4" t="s">
         <v>667</v>
       </c>
       <c r="N296" s="5" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="297" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A297" s="5" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D297" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E297" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H297" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I297" s="5" t="b">
         <v>0</v>
@@ -15020,33 +15006,33 @@
         <v>1</v>
       </c>
       <c r="L297" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M297" s="4" t="s">
         <v>668</v>
       </c>
       <c r="N297" s="5" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="298" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A298" s="5" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B298" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D298" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E298" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H298" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I298" s="5" t="b">
         <v>0</v>
@@ -15056,33 +15042,33 @@
         <v>1</v>
       </c>
       <c r="L298" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M298" s="4" t="s">
         <v>667</v>
       </c>
       <c r="N298" s="5" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="299" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A299" s="5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B299" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D299" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E299" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H299" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I299" s="5" t="b">
         <v>0</v>
@@ -15092,33 +15078,33 @@
         <v>1</v>
       </c>
       <c r="L299" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M299" s="4" t="s">
         <v>670</v>
       </c>
       <c r="N299" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="300" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A300" s="5" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B300" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="D300" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E300" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H300" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I300" s="5" t="b">
         <v>0</v>
@@ -15128,33 +15114,33 @@
         <v>1</v>
       </c>
       <c r="L300" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M300" s="4" t="s">
         <v>671</v>
       </c>
       <c r="N300" s="5" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="301" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A301" s="5" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B301" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D301" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E301" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H301" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I301" s="5" t="b">
         <v>0</v>
@@ -15164,33 +15150,33 @@
         <v>1</v>
       </c>
       <c r="L301" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M301" s="4" t="s">
         <v>668</v>
       </c>
       <c r="N301" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="302" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A302" s="5" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="B302" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D302" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E302" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H302" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I302" s="5" t="b">
         <v>0</v>
@@ -15200,33 +15186,33 @@
         <v>1</v>
       </c>
       <c r="L302" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="M302" s="4" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="N302" s="5" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="303" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A303" s="5" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D303" s="24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E303" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H303" s="5" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="I303" s="5" t="b">
         <v>0</v>
@@ -15246,22 +15232,22 @@
     </row>
     <row r="304" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A304" s="5" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="B304" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D304" s="24" t="s">
+        <v>804</v>
+      </c>
+      <c r="E304" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="H304" s="5" t="s">
         <v>807</v>
-      </c>
-      <c r="E304" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="H304" s="5" t="s">
-        <v>810</v>
       </c>
       <c r="I304" s="5" t="b">
         <v>0</v>
@@ -15274,30 +15260,30 @@
         <v>415</v>
       </c>
       <c r="M304" s="4" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="N304" s="5" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
     </row>
     <row r="305" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A305" s="5" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B305" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D305" s="24" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="E305" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H305" s="5" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="I305" s="5" t="b">
         <v>0</v>
@@ -15309,30 +15295,30 @@
         <v>555</v>
       </c>
       <c r="M305" s="4" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="N305" s="5" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="306" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B306" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="D306" s="24" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="E306" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H306" s="5" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="I306" s="5" t="b">
         <v>0</v>
@@ -15356,22 +15342,22 @@
     </row>
     <row r="307" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="B307" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C307" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="D307" s="24" t="s">
+        <v>820</v>
+      </c>
+      <c r="E307" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="H307" s="5" t="s">
         <v>821</v>
-      </c>
-      <c r="D307" s="24" t="s">
-        <v>823</v>
-      </c>
-      <c r="E307" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="H307" s="5" t="s">
-        <v>824</v>
       </c>
       <c r="I307" s="5" t="b">
         <v>0</v>
@@ -15395,22 +15381,22 @@
     </row>
     <row r="308" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B308" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="D308" s="24" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="E308" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H308" s="5" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="I308" s="5" t="b">
         <v>0</v>
@@ -15423,33 +15409,33 @@
         <v>1</v>
       </c>
       <c r="L308" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M308" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="N308" s="5" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="309" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A309" s="5" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B309" s="4" t="s">
         <v>56</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="D309" s="24" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="E309" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H309" s="5" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="I309" s="5" t="b">
         <v>0</v>
@@ -15461,33 +15447,33 @@
         <v>1</v>
       </c>
       <c r="L309" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M309" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="N309" s="47" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
     </row>
     <row r="310" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A310" s="5" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="B310" s="4" t="s">
         <v>56</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="D310" s="24" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="E310" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H310" s="5" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="I310" s="5" t="b">
         <v>0</v>
@@ -15499,33 +15485,33 @@
         <v>1</v>
       </c>
       <c r="L310" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M310" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="N310" s="47" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
     </row>
     <row r="311" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B311" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D311" s="24" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="E311" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H311" s="5" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="I311" s="5" t="b">
         <v>0</v>
@@ -15548,22 +15534,22 @@
     </row>
     <row r="312" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B312" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C312" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="D312" s="24" t="s">
         <v>851</v>
       </c>
-      <c r="D312" s="24" t="s">
-        <v>854</v>
-      </c>
       <c r="E312" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H312" s="5" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="I312" s="5" t="b">
         <v>0</v>
@@ -15586,22 +15572,22 @@
     </row>
     <row r="313" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="B313" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C313" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="D313" s="24" t="s">
+        <v>851</v>
+      </c>
+      <c r="E313" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="H313" s="5" t="s">
         <v>852</v>
-      </c>
-      <c r="D313" s="24" t="s">
-        <v>854</v>
-      </c>
-      <c r="E313" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="H313" s="5" t="s">
-        <v>855</v>
       </c>
       <c r="I313" s="5" t="b">
         <v>0</v>
@@ -15624,22 +15610,22 @@
     </row>
     <row r="314" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B314" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="D314" s="24" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="E314" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H314" s="5" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="I314" s="5" t="b">
         <v>0</v>
@@ -15662,23 +15648,23 @@
     </row>
     <row r="315" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B315" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="D315" s="24" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="E315" s="20" t="s">
         <v>345</v>
       </c>
       <c r="F315" s="46"/>
       <c r="H315" s="5" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="I315" s="5" t="b">
         <v>0</v>
@@ -15691,30 +15677,30 @@
         <v>111</v>
       </c>
       <c r="M315" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="N315" s="5" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
     </row>
     <row r="316" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="B316" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="D316" s="24" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="E316" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H316" s="5" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="I316" s="5" t="b">
         <v>0</v>
@@ -15737,22 +15723,22 @@
     </row>
     <row r="317" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B317" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C317" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="D317" s="24" t="s">
+        <v>876</v>
+      </c>
+      <c r="E317" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="H317" s="5" t="s">
         <v>886</v>
-      </c>
-      <c r="D317" s="24" t="s">
-        <v>879</v>
-      </c>
-      <c r="E317" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="H317" s="5" t="s">
-        <v>889</v>
       </c>
       <c r="I317" s="5" t="b">
         <v>0</v>
@@ -15775,22 +15761,22 @@
     </row>
     <row r="318" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="B318" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="D318" s="24" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="E318" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H318" s="5" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="I318" s="5" t="b">
         <v>0</v>
@@ -15813,22 +15799,22 @@
     </row>
     <row r="319" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B319" s="5" t="s">
         <v>563</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="D319" s="24" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="E319" s="20" t="s">
         <v>345</v>
       </c>
       <c r="H319" s="5" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="I319" s="5" t="b">
         <v>0</v>
@@ -15851,23 +15837,23 @@
     </row>
     <row r="320" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B320" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D320" s="24" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="E320" s="20" t="s">
         <v>345</v>
       </c>
       <c r="F320" s="46"/>
       <c r="H320" s="5" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="I320" s="5" t="b">
         <v>0</v>
@@ -15880,31 +15866,31 @@
         <v>111</v>
       </c>
       <c r="M320" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="N320" s="5" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
     </row>
     <row r="321" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B321" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="D321" s="24" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="E321" s="20" t="s">
         <v>345</v>
       </c>
       <c r="F321" s="46"/>
       <c r="H321" s="5" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="I321" s="5" t="b">
         <v>0</v>
@@ -15917,10 +15903,10 @@
         <v>111</v>
       </c>
       <c r="M321" s="4" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="N321" s="5" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
     </row>
   </sheetData>

--- a/work-in-progress/Peppol Code Lists - Document types v9.7.xlsx
+++ b/work-in-progress/Peppol Code Lists - Document types v9.7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philip/dev/git-peppol/edec-codelists/work-in-progress/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5AFE61-6A44-DE42-A483-007876BE5BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7423101D-3139-4146-A75C-2EE35F065866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2871" uniqueCount="900">
   <si>
     <t>urn:oasis:names:specification:ubl:schema:xsd:ApplicationResponse-2::ApplicationResponse##urn:www.cenbii.eu:transaction:biicoretrdm057:ver1.0:#urn:www.peppol.eu:bis:peppol1a:ver1.0::2.0</t>
   </si>
@@ -2834,6 +2834,18 @@
   <si>
     <t>TICC-365
 TICC-454</t>
+  </si>
+  <si>
+    <t>NLCIUS with SEeF extension v1.0</t>
+  </si>
+  <si>
+    <t>urn:oasis:names:specification:ubl:schema:xsd:Invoice-2::Invoice##urn:cen.eu:en16931:2017#compliant#urn:fdc:nen.nl:nlcius:v1.0#conformant#urn:fdc:energie-efactuur.nl:invoice:v3.0::2.1</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>TICC-456</t>
   </si>
 </sst>
 </file>
@@ -3506,7 +3518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F45987FB-91F4-488D-A9D3-2F3FAED3E07C}">
-  <dimension ref="A1:N321"/>
+  <dimension ref="A1:N322"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.5" style="5" bestFit="1" customWidth="1"/>
@@ -15909,6 +15921,42 @@
         <v>867</v>
       </c>
     </row>
+    <row r="322" spans="1:14" ht="48" x14ac:dyDescent="0.2">
+      <c r="A322" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="D322" s="23" t="s">
+        <v>898</v>
+      </c>
+      <c r="E322" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="H322" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="I322" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J322" s="5" t="b">
+        <f>FALSE</f>
+        <v>0</v>
+      </c>
+      <c r="L322" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="M322" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="N322" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N315" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
